--- a/artfynd/A 32128-2022 artfynd.xlsx
+++ b/artfynd/A 32128-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128344481</v>
       </c>
       <c r="B2" t="n">
-        <v>80163</v>
+        <v>80164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128344312</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128343815</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>128344369</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128343908</v>
       </c>
       <c r="B6" t="n">
-        <v>80163</v>
+        <v>80164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>128344214</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 32128-2022 artfynd.xlsx
+++ b/artfynd/A 32128-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128344481</v>
       </c>
       <c r="B2" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128344312</v>
       </c>
       <c r="B3" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128343815</v>
       </c>
       <c r="B4" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>128344369</v>
       </c>
       <c r="B5" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128343908</v>
       </c>
       <c r="B6" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>128344214</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 32128-2022 artfynd.xlsx
+++ b/artfynd/A 32128-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128344481</v>
       </c>
       <c r="B2" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128344312</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128343815</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>128344369</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128343908</v>
       </c>
       <c r="B6" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>128344214</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 32128-2022 artfynd.xlsx
+++ b/artfynd/A 32128-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128344481</v>
       </c>
       <c r="B2" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128343908</v>
       </c>
       <c r="B6" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32128-2022 artfynd.xlsx
+++ b/artfynd/A 32128-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128344481</v>
       </c>
       <c r="B2" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128344312</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128343815</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>128344369</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128343908</v>
       </c>
       <c r="B6" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>128344214</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
